--- a/tests/fixtures/2019-2025 SDN Children in Armed Conflict Incident Data.xlsx
+++ b/tests/fixtures/2019-2025 SDN Children in Armed Conflict Incident Data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1331" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1331" uniqueCount="230">
   <si>
     <t>Date</t>
   </si>
@@ -121,19 +121,7 @@
     <t>Red Sea State</t>
   </si>
   <si>
-    <t xml:space="preserve">(2) 25 km Precision </t>
-  </si>
-  <si>
-    <t xml:space="preserve">(3) District, Communicipality or Commune </t>
-  </si>
-  <si>
-    <t xml:space="preserve">(5) Linear Feature e.g. Along Road/River </t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4) Province, State, Governorate </t>
-  </si>
-  <si>
-    <t>(6) Country</t>
+    <t>censored</t>
   </si>
   <si>
     <t>Vigilante</t>
@@ -1111,26 +1099,20 @@
       <c r="E2" t="s">
         <v>16</v>
       </c>
-      <c r="F2">
-        <v>15</v>
-      </c>
-      <c r="G2">
-        <v>23.2</v>
-      </c>
       <c r="H2" t="s">
         <v>35</v>
       </c>
       <c r="I2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="L2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="M2" s="1">
         <v>45987</v>
@@ -1152,26 +1134,20 @@
       <c r="E3" t="s">
         <v>16</v>
       </c>
-      <c r="F3">
-        <v>13.6</v>
-      </c>
-      <c r="G3">
-        <v>25.3</v>
-      </c>
       <c r="H3" t="s">
         <v>35</v>
       </c>
       <c r="I3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="M3" s="1">
         <v>45987</v>
@@ -1193,26 +1169,20 @@
       <c r="E4" t="s">
         <v>17</v>
       </c>
-      <c r="F4">
-        <v>12</v>
-      </c>
-      <c r="G4">
-        <v>24.9</v>
-      </c>
       <c r="H4" t="s">
         <v>35</v>
       </c>
       <c r="I4" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="L4" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="M4" s="1">
         <v>45986</v>
@@ -1234,26 +1204,20 @@
       <c r="E5" t="s">
         <v>16</v>
       </c>
-      <c r="F5">
-        <v>13.6</v>
-      </c>
-      <c r="G5">
-        <v>25.3</v>
-      </c>
       <c r="H5" t="s">
         <v>35</v>
       </c>
       <c r="I5" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L5" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="M5" s="1">
         <v>45987</v>
@@ -1275,26 +1239,20 @@
       <c r="E6" t="s">
         <v>16</v>
       </c>
-      <c r="F6">
-        <v>13.6</v>
-      </c>
-      <c r="G6">
-        <v>25.3</v>
-      </c>
       <c r="H6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J6" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K6" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L6" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M6" s="1">
         <v>45988</v>
@@ -1316,26 +1274,20 @@
       <c r="E7" t="s">
         <v>18</v>
       </c>
-      <c r="F7">
-        <v>15.5</v>
-      </c>
-      <c r="G7">
-        <v>32.4</v>
-      </c>
       <c r="H7" t="s">
         <v>35</v>
       </c>
       <c r="I7" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J7" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K7" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="L7" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="M7" s="1">
         <v>45986</v>
@@ -1357,26 +1309,20 @@
       <c r="E8" t="s">
         <v>16</v>
       </c>
-      <c r="F8">
-        <v>13.6</v>
-      </c>
-      <c r="G8">
-        <v>25.3</v>
-      </c>
       <c r="H8" t="s">
         <v>35</v>
       </c>
       <c r="I8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J8" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K8" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="L8" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="M8" s="1">
         <v>45963</v>
@@ -1398,26 +1344,20 @@
       <c r="E9" t="s">
         <v>19</v>
       </c>
-      <c r="F9">
-        <v>14.7</v>
-      </c>
-      <c r="G9">
-        <v>33.3</v>
-      </c>
       <c r="H9" t="s">
         <v>35</v>
       </c>
       <c r="I9" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="J9" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="K9" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L9" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="M9" s="1">
         <v>45979</v>
@@ -1439,26 +1379,20 @@
       <c r="E10" t="s">
         <v>16</v>
       </c>
-      <c r="F10">
-        <v>13.6</v>
-      </c>
-      <c r="G10">
-        <v>25.3</v>
-      </c>
       <c r="H10" t="s">
         <v>35</v>
       </c>
       <c r="I10" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J10" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K10" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L10" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="M10" s="1">
         <v>45963</v>
@@ -1480,26 +1414,20 @@
       <c r="E11" t="s">
         <v>20</v>
       </c>
-      <c r="F11">
-        <v>12.2</v>
-      </c>
-      <c r="G11">
-        <v>24.7</v>
-      </c>
       <c r="H11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I11" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J11" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K11" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L11" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="M11" s="1">
         <v>45979</v>
@@ -1521,26 +1449,20 @@
       <c r="E12" t="s">
         <v>16</v>
       </c>
-      <c r="F12">
-        <v>13.6</v>
-      </c>
-      <c r="G12">
-        <v>25.3</v>
-      </c>
       <c r="H12" t="s">
         <v>35</v>
       </c>
       <c r="I12" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J12" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K12" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L12" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="M12" s="1">
         <v>45945</v>
@@ -1562,26 +1484,20 @@
       <c r="E13" t="s">
         <v>16</v>
       </c>
-      <c r="F13">
-        <v>13.6</v>
-      </c>
-      <c r="G13">
-        <v>25.3</v>
-      </c>
       <c r="H13" t="s">
         <v>35</v>
       </c>
       <c r="I13" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J13" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K13" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L13" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="M13" s="1">
         <v>45944</v>
@@ -1603,26 +1519,20 @@
       <c r="E14" t="s">
         <v>21</v>
       </c>
-      <c r="F14">
-        <v>11.9</v>
-      </c>
-      <c r="G14">
-        <v>30</v>
-      </c>
       <c r="H14" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I14" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J14" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K14" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L14" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="M14" s="1">
         <v>45956</v>
@@ -1644,26 +1554,20 @@
       <c r="E15" t="s">
         <v>16</v>
       </c>
-      <c r="F15">
-        <v>13.6</v>
-      </c>
-      <c r="G15">
-        <v>25.3</v>
-      </c>
       <c r="H15" t="s">
         <v>35</v>
       </c>
       <c r="I15" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J15" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K15" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="L15" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="M15" s="1">
         <v>45922</v>
@@ -1685,26 +1589,20 @@
       <c r="E16" t="s">
         <v>16</v>
       </c>
-      <c r="F16">
-        <v>13.6</v>
-      </c>
-      <c r="G16">
-        <v>25.3</v>
-      </c>
       <c r="H16" t="s">
         <v>35</v>
       </c>
       <c r="I16" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J16" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K16" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="L16" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="M16" s="1">
         <v>45938</v>
@@ -1726,26 +1624,20 @@
       <c r="E17" t="s">
         <v>16</v>
       </c>
-      <c r="F17">
-        <v>13.6</v>
-      </c>
-      <c r="G17">
-        <v>25.3</v>
-      </c>
       <c r="H17" t="s">
         <v>35</v>
       </c>
       <c r="I17" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J17" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K17" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="L17" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="M17" s="1">
         <v>45938</v>
@@ -1767,26 +1659,20 @@
       <c r="E18" t="s">
         <v>16</v>
       </c>
-      <c r="F18">
-        <v>13.6</v>
-      </c>
-      <c r="G18">
-        <v>25.3</v>
-      </c>
       <c r="H18" t="s">
         <v>35</v>
       </c>
       <c r="I18" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J18" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K18" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L18" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="M18" s="1">
         <v>45917</v>
@@ -1808,26 +1694,20 @@
       <c r="E19" t="s">
         <v>16</v>
       </c>
-      <c r="F19">
-        <v>13.6</v>
-      </c>
-      <c r="G19">
-        <v>25.3</v>
-      </c>
       <c r="H19" t="s">
         <v>35</v>
       </c>
       <c r="I19" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J19" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K19" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L19" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M19" s="1">
         <v>45917</v>
@@ -1849,26 +1729,20 @@
       <c r="E20" t="s">
         <v>22</v>
       </c>
-      <c r="F20">
-        <v>11.4</v>
-      </c>
-      <c r="G20">
-        <v>26.1</v>
-      </c>
       <c r="H20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I20" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J20" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K20" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="L20" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M20" s="1">
         <v>45938</v>
@@ -1890,26 +1764,20 @@
       <c r="E21" t="s">
         <v>23</v>
       </c>
-      <c r="F21">
-        <v>11.7</v>
-      </c>
-      <c r="G21">
-        <v>28.2</v>
-      </c>
       <c r="H21" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I21" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="J21" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="K21" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L21" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="M21" s="1">
         <v>45903</v>
@@ -1931,26 +1799,20 @@
       <c r="E22" t="s">
         <v>23</v>
       </c>
-      <c r="F22">
-        <v>12.3</v>
-      </c>
-      <c r="G22">
-        <v>29.2</v>
-      </c>
       <c r="H22" t="s">
         <v>35</v>
       </c>
       <c r="I22" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="J22" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="K22" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L22" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="M22" s="1">
         <v>45924</v>
@@ -1972,26 +1834,20 @@
       <c r="E23" t="s">
         <v>23</v>
       </c>
-      <c r="F23">
-        <v>12.3</v>
-      </c>
-      <c r="G23">
-        <v>29.2</v>
-      </c>
       <c r="H23" t="s">
         <v>35</v>
       </c>
       <c r="I23" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="J23" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="K23" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L23" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="M23" s="1">
         <v>45924</v>
@@ -2013,26 +1869,20 @@
       <c r="E24" t="s">
         <v>24</v>
       </c>
-      <c r="F24">
-        <v>13.6</v>
-      </c>
-      <c r="G24">
-        <v>30.3</v>
-      </c>
       <c r="H24" t="s">
         <v>35</v>
       </c>
       <c r="I24" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J24" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K24" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L24" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="M24" s="1">
         <v>45924</v>
@@ -2054,26 +1904,20 @@
       <c r="E25" t="s">
         <v>23</v>
       </c>
-      <c r="F25">
-        <v>11</v>
-      </c>
-      <c r="G25">
-        <v>27.7</v>
-      </c>
       <c r="H25" t="s">
         <v>35</v>
       </c>
       <c r="I25" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J25" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K25" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="L25" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="M25" s="1">
         <v>45856</v>
@@ -2095,26 +1939,20 @@
       <c r="E26" t="s">
         <v>16</v>
       </c>
-      <c r="F26">
-        <v>13.6</v>
-      </c>
-      <c r="G26">
-        <v>25.3</v>
-      </c>
       <c r="H26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I26" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J26" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K26" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="L26" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M26" s="1">
         <v>45920</v>
@@ -2136,26 +1974,20 @@
       <c r="E27" t="s">
         <v>23</v>
       </c>
-      <c r="F27">
-        <v>12.3</v>
-      </c>
-      <c r="G27">
-        <v>29.2</v>
-      </c>
       <c r="H27" t="s">
         <v>35</v>
       </c>
       <c r="I27" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="J27" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="K27" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L27" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="M27" s="1">
         <v>45875</v>
@@ -2174,26 +2006,20 @@
       <c r="D28" t="s">
         <v>15</v>
       </c>
-      <c r="F28">
-        <v>15</v>
-      </c>
-      <c r="G28">
-        <v>32</v>
-      </c>
       <c r="H28" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I28" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J28" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K28" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L28" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M28" s="1">
         <v>45856</v>
@@ -2215,26 +2041,20 @@
       <c r="E29" t="s">
         <v>16</v>
       </c>
-      <c r="F29">
-        <v>13.6</v>
-      </c>
-      <c r="G29">
-        <v>25.3</v>
-      </c>
       <c r="H29" t="s">
         <v>35</v>
       </c>
       <c r="I29" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J29" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K29" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="L29" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="M29" s="1">
         <v>45868</v>
@@ -2256,26 +2076,20 @@
       <c r="E30" t="s">
         <v>20</v>
       </c>
-      <c r="F30">
-        <v>12</v>
-      </c>
-      <c r="G30">
-        <v>24.9</v>
-      </c>
       <c r="H30" t="s">
         <v>35</v>
       </c>
       <c r="I30" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J30" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K30" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="L30" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="M30" s="1">
         <v>45868</v>
@@ -2297,26 +2111,20 @@
       <c r="E31" t="s">
         <v>24</v>
       </c>
-      <c r="F31">
-        <v>13.5</v>
-      </c>
-      <c r="G31">
-        <v>30.3</v>
-      </c>
       <c r="H31" t="s">
         <v>35</v>
       </c>
       <c r="I31" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J31" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K31" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L31" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M31" s="1">
         <v>45854</v>
@@ -2338,26 +2146,20 @@
       <c r="E32" t="s">
         <v>21</v>
       </c>
-      <c r="F32">
-        <v>11</v>
-      </c>
-      <c r="G32">
-        <v>31</v>
-      </c>
       <c r="H32" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I32" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J32" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K32" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L32" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="M32" s="1">
         <v>45903</v>
@@ -2376,26 +2178,20 @@
       <c r="D33" t="s">
         <v>15</v>
       </c>
-      <c r="F33">
-        <v>15</v>
-      </c>
-      <c r="G33">
-        <v>32</v>
-      </c>
       <c r="H33" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I33" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J33" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K33" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L33" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="M33" s="1">
         <v>45818</v>
@@ -2417,26 +2213,20 @@
       <c r="E34" t="s">
         <v>16</v>
       </c>
-      <c r="F34">
-        <v>13.4</v>
-      </c>
-      <c r="G34">
-        <v>25.3</v>
-      </c>
       <c r="H34" t="s">
         <v>35</v>
       </c>
       <c r="I34" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J34" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K34" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L34" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="M34" s="1">
         <v>45817</v>
@@ -2458,26 +2248,20 @@
       <c r="E35" t="s">
         <v>25</v>
       </c>
-      <c r="F35">
-        <v>15.5</v>
-      </c>
-      <c r="G35">
-        <v>32.5</v>
-      </c>
       <c r="H35" t="s">
         <v>35</v>
       </c>
       <c r="I35" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J35" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K35" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L35" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="M35" s="1">
         <v>45825</v>
@@ -2499,26 +2283,20 @@
       <c r="E36" t="s">
         <v>16</v>
       </c>
-      <c r="F36">
-        <v>13.4</v>
-      </c>
-      <c r="G36">
-        <v>25.3</v>
-      </c>
       <c r="H36" t="s">
         <v>35</v>
       </c>
       <c r="I36" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J36" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K36" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L36" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="M36" s="1">
         <v>45858</v>
@@ -2540,26 +2318,20 @@
       <c r="E37" t="s">
         <v>16</v>
       </c>
-      <c r="F37">
-        <v>13.6</v>
-      </c>
-      <c r="G37">
-        <v>25.3</v>
-      </c>
       <c r="H37" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I37" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J37" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K37" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="L37" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="M37" s="1">
         <v>45839</v>
@@ -2581,26 +2353,20 @@
       <c r="E38" t="s">
         <v>16</v>
       </c>
-      <c r="F38">
-        <v>13.6</v>
-      </c>
-      <c r="G38">
-        <v>25.3</v>
-      </c>
       <c r="H38" t="s">
         <v>35</v>
       </c>
       <c r="I38" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J38" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K38" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="L38" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="M38" s="1">
         <v>45817</v>
@@ -2622,26 +2388,20 @@
       <c r="E39" t="s">
         <v>16</v>
       </c>
-      <c r="F39">
-        <v>13</v>
-      </c>
-      <c r="G39">
-        <v>25.7</v>
-      </c>
       <c r="H39" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I39" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J39" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K39" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L39" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="M39" s="1">
         <v>45817</v>
@@ -2663,26 +2423,20 @@
       <c r="E40" t="s">
         <v>24</v>
       </c>
-      <c r="F40">
-        <v>12.9</v>
-      </c>
-      <c r="G40">
-        <v>31.4</v>
-      </c>
       <c r="H40" t="s">
         <v>35</v>
       </c>
       <c r="I40" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J40" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="K40" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="L40" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="M40" s="1">
         <v>45875</v>
@@ -2704,26 +2458,20 @@
       <c r="E41" t="s">
         <v>16</v>
       </c>
-      <c r="F41">
-        <v>13.4</v>
-      </c>
-      <c r="G41">
-        <v>25.3</v>
-      </c>
       <c r="H41" t="s">
         <v>35</v>
       </c>
       <c r="I41" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="J41" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="K41" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="L41" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="M41" s="1">
         <v>45792</v>
@@ -2745,26 +2493,20 @@
       <c r="E42" t="s">
         <v>25</v>
       </c>
-      <c r="F42">
-        <v>15.5</v>
-      </c>
-      <c r="G42">
-        <v>32.5</v>
-      </c>
       <c r="H42" t="s">
         <v>35</v>
       </c>
       <c r="I42" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J42" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K42" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L42" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="M42" s="1">
         <v>45807</v>
@@ -2786,26 +2528,20 @@
       <c r="E43" t="s">
         <v>25</v>
       </c>
-      <c r="F43">
-        <v>15.6</v>
-      </c>
-      <c r="G43">
-        <v>32.4</v>
-      </c>
       <c r="H43" t="s">
         <v>35</v>
       </c>
       <c r="I43" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J43" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K43" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L43" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="M43" s="1">
         <v>45798</v>
@@ -2827,26 +2563,20 @@
       <c r="E44" t="s">
         <v>25</v>
       </c>
-      <c r="F44">
-        <v>15.6</v>
-      </c>
-      <c r="G44">
-        <v>32.6</v>
-      </c>
       <c r="H44" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I44" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J44" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K44" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L44" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="M44" s="1">
         <v>45744</v>
@@ -2868,26 +2598,20 @@
       <c r="E45" t="s">
         <v>16</v>
       </c>
-      <c r="F45">
-        <v>16</v>
-      </c>
-      <c r="G45">
-        <v>26</v>
-      </c>
       <c r="H45" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I45" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J45" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K45" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L45" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="M45" s="1">
         <v>45744</v>
@@ -2909,26 +2633,20 @@
       <c r="E46" t="s">
         <v>16</v>
       </c>
-      <c r="F46">
-        <v>13.9</v>
-      </c>
-      <c r="G46">
-        <v>26</v>
-      </c>
       <c r="H46" t="s">
         <v>35</v>
       </c>
       <c r="I46" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="J46" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="K46" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L46" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="M46" s="1">
         <v>45778</v>
@@ -2950,26 +2668,20 @@
       <c r="E47" t="s">
         <v>24</v>
       </c>
-      <c r="F47">
-        <v>13.1</v>
-      </c>
-      <c r="G47">
-        <v>30.2</v>
-      </c>
       <c r="H47" t="s">
         <v>35</v>
       </c>
       <c r="I47" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J47" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K47" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L47" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="M47" s="1">
         <v>45747</v>
@@ -2991,26 +2703,20 @@
       <c r="E48" t="s">
         <v>16</v>
       </c>
-      <c r="F48">
-        <v>16</v>
-      </c>
-      <c r="G48">
-        <v>26</v>
-      </c>
       <c r="H48" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I48" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J48" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K48" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L48" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="M48" s="1">
         <v>45744</v>
@@ -3032,26 +2738,20 @@
       <c r="E49" t="s">
         <v>26</v>
       </c>
-      <c r="F49">
-        <v>13</v>
-      </c>
-      <c r="G49">
-        <v>23.6</v>
-      </c>
       <c r="H49" t="s">
         <v>35</v>
       </c>
       <c r="I49" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="J49" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="K49" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L49" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="M49" s="1">
         <v>45753</v>
@@ -3073,26 +2773,20 @@
       <c r="E50" t="s">
         <v>16</v>
       </c>
-      <c r="F50">
-        <v>13.6</v>
-      </c>
-      <c r="G50">
-        <v>25.3</v>
-      </c>
       <c r="H50" t="s">
         <v>35</v>
       </c>
       <c r="I50" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J50" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K50" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L50" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="M50" s="1">
         <v>45709</v>
@@ -3114,26 +2808,20 @@
       <c r="E51" t="s">
         <v>25</v>
       </c>
-      <c r="F51">
-        <v>15.6</v>
-      </c>
-      <c r="G51">
-        <v>32.4</v>
-      </c>
       <c r="H51" t="s">
         <v>35</v>
       </c>
       <c r="I51" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J51" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K51" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L51" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="M51" s="1">
         <v>45726</v>
@@ -3155,26 +2843,20 @@
       <c r="E52" t="s">
         <v>25</v>
       </c>
-      <c r="F52">
-        <v>15.6</v>
-      </c>
-      <c r="G52">
-        <v>32.5</v>
-      </c>
       <c r="H52" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I52" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J52" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K52" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L52" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="M52" s="1">
         <v>45727</v>
@@ -3196,26 +2878,20 @@
       <c r="E53" t="s">
         <v>16</v>
       </c>
-      <c r="F53">
-        <v>13.6</v>
-      </c>
-      <c r="G53">
-        <v>25.3</v>
-      </c>
       <c r="H53" t="s">
         <v>35</v>
       </c>
       <c r="I53" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J53" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K53" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L53" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="M53" s="1">
         <v>45690</v>
@@ -3237,26 +2913,20 @@
       <c r="E54" t="s">
         <v>16</v>
       </c>
-      <c r="F54">
-        <v>13.6</v>
-      </c>
-      <c r="G54">
-        <v>25.3</v>
-      </c>
       <c r="H54" t="s">
         <v>35</v>
       </c>
       <c r="I54" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="J54" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="K54" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="L54" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="M54" s="1">
         <v>45718</v>
@@ -3278,26 +2948,20 @@
       <c r="E55" t="s">
         <v>16</v>
       </c>
-      <c r="F55">
-        <v>13.6</v>
-      </c>
-      <c r="G55">
-        <v>25.3</v>
-      </c>
       <c r="H55" t="s">
         <v>35</v>
       </c>
       <c r="I55" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J55" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K55" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L55" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="M55" s="1">
         <v>45726</v>
@@ -3319,26 +2983,20 @@
       <c r="E56" t="s">
         <v>16</v>
       </c>
-      <c r="F56">
-        <v>13.4</v>
-      </c>
-      <c r="G56">
-        <v>25.4</v>
-      </c>
       <c r="H56" t="s">
         <v>35</v>
       </c>
       <c r="I56" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J56" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K56" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L56" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="M56" s="1">
         <v>45660</v>
@@ -3360,26 +3018,20 @@
       <c r="E57" t="s">
         <v>16</v>
       </c>
-      <c r="F57">
-        <v>13.6</v>
-      </c>
-      <c r="G57">
-        <v>25.3</v>
-      </c>
       <c r="H57" t="s">
         <v>35</v>
       </c>
       <c r="I57" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J57" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K57" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L57" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="M57" s="1">
         <v>45690</v>
@@ -3401,26 +3053,20 @@
       <c r="E58" t="s">
         <v>16</v>
       </c>
-      <c r="F58">
-        <v>13.6</v>
-      </c>
-      <c r="G58">
-        <v>25.3</v>
-      </c>
       <c r="H58" t="s">
         <v>35</v>
       </c>
       <c r="I58" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J58" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K58" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L58" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="M58" s="1">
         <v>45679</v>
@@ -3442,26 +3088,20 @@
       <c r="E59" t="s">
         <v>20</v>
       </c>
-      <c r="F59">
-        <v>12</v>
-      </c>
-      <c r="G59">
-        <v>24.8</v>
-      </c>
       <c r="H59" t="s">
         <v>35</v>
       </c>
       <c r="I59" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="J59" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="K59" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="L59" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="M59" s="1">
         <v>45685</v>
@@ -3483,26 +3123,20 @@
       <c r="E60" t="s">
         <v>16</v>
       </c>
-      <c r="F60">
-        <v>13.6</v>
-      </c>
-      <c r="G60">
-        <v>25.3</v>
-      </c>
       <c r="H60" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I60" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J60" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K60" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="L60" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="M60" s="1">
         <v>45687</v>
@@ -3524,26 +3158,20 @@
       <c r="E61" t="s">
         <v>16</v>
       </c>
-      <c r="F61">
-        <v>13.6</v>
-      </c>
-      <c r="G61">
-        <v>25.3</v>
-      </c>
       <c r="H61" t="s">
         <v>35</v>
       </c>
       <c r="I61" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J61" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K61" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L61" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="M61" s="1">
         <v>45661</v>
@@ -3565,26 +3193,20 @@
       <c r="E62" t="s">
         <v>16</v>
       </c>
-      <c r="F62">
-        <v>13.4</v>
-      </c>
-      <c r="G62">
-        <v>25.3</v>
-      </c>
       <c r="H62" t="s">
         <v>35</v>
       </c>
       <c r="I62" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J62" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K62" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="L62" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="M62" s="1">
         <v>45687</v>
@@ -3606,26 +3228,20 @@
       <c r="E63" t="s">
         <v>18</v>
       </c>
-      <c r="F63">
-        <v>15.6</v>
-      </c>
-      <c r="G63">
-        <v>32.4</v>
-      </c>
       <c r="H63" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I63" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J63" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K63" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="L63" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="M63" s="1">
         <v>45685</v>
@@ -3647,26 +3263,20 @@
       <c r="E64" t="s">
         <v>16</v>
       </c>
-      <c r="F64">
-        <v>13.4</v>
-      </c>
-      <c r="G64">
-        <v>25.3</v>
-      </c>
       <c r="H64" t="s">
         <v>35</v>
       </c>
       <c r="I64" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J64" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K64" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="L64" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="M64" s="1">
         <v>45687</v>
@@ -3688,26 +3298,20 @@
       <c r="E65" t="s">
         <v>16</v>
       </c>
-      <c r="F65">
-        <v>13.4</v>
-      </c>
-      <c r="G65">
-        <v>25.3</v>
-      </c>
       <c r="H65" t="s">
         <v>35</v>
       </c>
       <c r="I65" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J65" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K65" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="L65" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="M65" s="1">
         <v>45693</v>
@@ -3729,26 +3333,20 @@
       <c r="E66" t="s">
         <v>16</v>
       </c>
-      <c r="F66">
-        <v>13.4</v>
-      </c>
-      <c r="G66">
-        <v>25.3</v>
-      </c>
       <c r="H66" t="s">
         <v>35</v>
       </c>
       <c r="I66" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J66" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K66" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="L66" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="M66" s="1">
         <v>45693</v>
@@ -3770,26 +3368,20 @@
       <c r="E67" t="s">
         <v>27</v>
       </c>
-      <c r="F67">
-        <v>13.5</v>
-      </c>
-      <c r="G67">
-        <v>33.6</v>
-      </c>
       <c r="H67" t="s">
         <v>35</v>
       </c>
       <c r="I67" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J67" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K67" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L67" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="M67" s="1">
         <v>45677</v>
@@ -3811,26 +3403,20 @@
       <c r="E68" t="s">
         <v>16</v>
       </c>
-      <c r="F68">
-        <v>13.4</v>
-      </c>
-      <c r="G68">
-        <v>25.3</v>
-      </c>
       <c r="H68" t="s">
         <v>35</v>
       </c>
       <c r="I68" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J68" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K68" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="L68" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="M68" s="1">
         <v>45687</v>
@@ -3852,26 +3438,20 @@
       <c r="E69" t="s">
         <v>28</v>
       </c>
-      <c r="F69">
-        <v>13.3</v>
-      </c>
-      <c r="G69">
-        <v>22.7</v>
-      </c>
       <c r="H69" t="s">
         <v>35</v>
       </c>
       <c r="I69" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="J69" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="K69" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L69" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="M69" s="1">
         <v>45677</v>
@@ -3893,26 +3473,20 @@
       <c r="E70" t="s">
         <v>16</v>
       </c>
-      <c r="F70">
-        <v>13.9</v>
-      </c>
-      <c r="G70">
-        <v>24.9</v>
-      </c>
       <c r="H70" t="s">
         <v>35</v>
       </c>
       <c r="I70" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="J70" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="K70" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L70" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="M70" s="1">
         <v>45676</v>
@@ -3934,26 +3508,20 @@
       <c r="E71" t="s">
         <v>16</v>
       </c>
-      <c r="F71">
-        <v>16</v>
-      </c>
-      <c r="G71">
-        <v>26</v>
-      </c>
       <c r="H71" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I71" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J71" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K71" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L71" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="M71" s="1">
         <v>45697</v>
@@ -3975,26 +3543,20 @@
       <c r="E72" t="s">
         <v>29</v>
       </c>
-      <c r="F72">
-        <v>14.6</v>
-      </c>
-      <c r="G72">
-        <v>33.2</v>
-      </c>
       <c r="H72" t="s">
         <v>35</v>
       </c>
       <c r="I72" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J72" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K72" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L72" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M72" s="1">
         <v>45693</v>
@@ -4016,26 +3578,20 @@
       <c r="E73" t="s">
         <v>29</v>
       </c>
-      <c r="F73">
-        <v>14.6</v>
-      </c>
-      <c r="G73">
-        <v>33.2</v>
-      </c>
       <c r="H73" t="s">
         <v>35</v>
       </c>
       <c r="I73" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J73" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K73" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L73" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M73" s="1">
         <v>45693</v>
@@ -4057,26 +3613,20 @@
       <c r="E74" t="s">
         <v>20</v>
       </c>
-      <c r="F74">
-        <v>12</v>
-      </c>
-      <c r="G74">
-        <v>24.8</v>
-      </c>
       <c r="H74" t="s">
         <v>35</v>
       </c>
       <c r="I74" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J74" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K74" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L74" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="M74" s="1">
         <v>45639</v>
@@ -4098,26 +3648,20 @@
       <c r="E75" t="s">
         <v>29</v>
       </c>
-      <c r="F75">
-        <v>14.9</v>
-      </c>
-      <c r="G75">
-        <v>33.2</v>
-      </c>
       <c r="H75" t="s">
         <v>35</v>
       </c>
       <c r="I75" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J75" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K75" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L75" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="M75" s="1">
         <v>45683</v>
@@ -4139,26 +3683,20 @@
       <c r="E76" t="s">
         <v>29</v>
       </c>
-      <c r="F76">
-        <v>14.6</v>
-      </c>
-      <c r="G76">
-        <v>33.2</v>
-      </c>
       <c r="H76" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I76" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J76" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K76" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L76" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="M76" s="1">
         <v>45683</v>
@@ -4180,26 +3718,20 @@
       <c r="E77" t="s">
         <v>27</v>
       </c>
-      <c r="F77">
-        <v>13.1</v>
-      </c>
-      <c r="G77">
-        <v>33.9</v>
-      </c>
       <c r="H77" t="s">
         <v>35</v>
       </c>
       <c r="I77" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J77" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K77" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L77" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="M77" s="1">
         <v>45620</v>
@@ -4218,26 +3750,20 @@
       <c r="D78" t="s">
         <v>15</v>
       </c>
-      <c r="F78">
-        <v>15</v>
-      </c>
-      <c r="G78">
-        <v>32</v>
-      </c>
       <c r="H78" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I78" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J78" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K78" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L78" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M78" s="1">
         <v>45683</v>
@@ -4259,26 +3785,20 @@
       <c r="E79" t="s">
         <v>16</v>
       </c>
-      <c r="F79">
-        <v>13.6</v>
-      </c>
-      <c r="G79">
-        <v>25.3</v>
-      </c>
       <c r="H79" t="s">
         <v>35</v>
       </c>
       <c r="I79" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J79" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K79" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L79" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="M79" s="1">
         <v>45602</v>
@@ -4300,26 +3820,20 @@
       <c r="E80" t="s">
         <v>25</v>
       </c>
-      <c r="F80">
-        <v>15.4</v>
-      </c>
-      <c r="G80">
-        <v>32.4</v>
-      </c>
       <c r="H80" t="s">
         <v>35</v>
       </c>
       <c r="I80" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J80" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K80" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="L80" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="M80" s="1">
         <v>45619</v>
@@ -4341,26 +3855,20 @@
       <c r="E81" t="s">
         <v>16</v>
       </c>
-      <c r="F81">
-        <v>14.3</v>
-      </c>
-      <c r="G81">
-        <v>25.7</v>
-      </c>
       <c r="H81" t="s">
         <v>35</v>
       </c>
       <c r="I81" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J81" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K81" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L81" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="M81" s="1">
         <v>45630</v>
@@ -4382,26 +3890,20 @@
       <c r="E82" t="s">
         <v>16</v>
       </c>
-      <c r="F82">
-        <v>13.6</v>
-      </c>
-      <c r="G82">
-        <v>25.3</v>
-      </c>
       <c r="H82" t="s">
         <v>35</v>
       </c>
       <c r="I82" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J82" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K82" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="L82" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="M82" s="1">
         <v>45637</v>
@@ -4423,26 +3925,20 @@
       <c r="E83" t="s">
         <v>18</v>
       </c>
-      <c r="F83">
-        <v>15.6</v>
-      </c>
-      <c r="G83">
-        <v>32.4</v>
-      </c>
       <c r="H83" t="s">
         <v>35</v>
       </c>
       <c r="I83" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J83" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K83" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="L83" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="M83" s="1">
         <v>45637</v>
@@ -4464,26 +3960,20 @@
       <c r="E84" t="s">
         <v>27</v>
       </c>
-      <c r="F84">
-        <v>13.1</v>
-      </c>
-      <c r="G84">
-        <v>33.9</v>
-      </c>
       <c r="H84" t="s">
         <v>35</v>
       </c>
       <c r="I84" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J84" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K84" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L84" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="M84" s="1">
         <v>45574</v>
@@ -4505,26 +3995,20 @@
       <c r="E85" t="s">
         <v>16</v>
       </c>
-      <c r="F85">
-        <v>13.6</v>
-      </c>
-      <c r="G85">
-        <v>25.3</v>
-      </c>
       <c r="H85" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I85" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J85" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K85" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L85" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="M85" s="1">
         <v>45615</v>
@@ -4546,26 +4030,20 @@
       <c r="E86" t="s">
         <v>26</v>
       </c>
-      <c r="F86">
-        <v>13</v>
-      </c>
-      <c r="G86">
-        <v>23.6</v>
-      </c>
       <c r="H86" t="s">
         <v>35</v>
       </c>
       <c r="I86" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J86" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K86" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L86" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="M86" s="1">
         <v>45586</v>
@@ -4587,26 +4065,20 @@
       <c r="E87" t="s">
         <v>20</v>
       </c>
-      <c r="F87">
-        <v>12</v>
-      </c>
-      <c r="G87">
-        <v>24.8</v>
-      </c>
       <c r="H87" t="s">
         <v>35</v>
       </c>
       <c r="I87" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="J87" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="K87" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L87" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="M87" s="1">
         <v>45574</v>
@@ -4628,26 +4100,20 @@
       <c r="E88" t="s">
         <v>20</v>
       </c>
-      <c r="F88">
-        <v>12</v>
-      </c>
-      <c r="G88">
-        <v>24.8</v>
-      </c>
       <c r="H88" t="s">
         <v>35</v>
       </c>
       <c r="I88" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="J88" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="K88" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L88" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M88" s="1">
         <v>45574</v>
@@ -4669,26 +4135,20 @@
       <c r="E89" t="s">
         <v>16</v>
       </c>
-      <c r="F89">
-        <v>13.6</v>
-      </c>
-      <c r="G89">
-        <v>25.3</v>
-      </c>
       <c r="H89" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I89" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J89" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K89" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L89" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="M89" s="1">
         <v>45615</v>
@@ -4710,26 +4170,20 @@
       <c r="E90" t="s">
         <v>25</v>
       </c>
-      <c r="F90">
-        <v>15.6</v>
-      </c>
-      <c r="G90">
-        <v>32.4</v>
-      </c>
       <c r="H90" t="s">
         <v>35</v>
       </c>
       <c r="I90" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J90" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K90" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L90" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="M90" s="1">
         <v>45574</v>
@@ -4751,26 +4205,20 @@
       <c r="E91" t="s">
         <v>16</v>
       </c>
-      <c r="F91">
-        <v>13.6</v>
-      </c>
-      <c r="G91">
-        <v>25.3</v>
-      </c>
       <c r="H91" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I91" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J91" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K91" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L91" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="M91" s="1">
         <v>45548</v>
@@ -4792,26 +4240,20 @@
       <c r="E92" t="s">
         <v>16</v>
       </c>
-      <c r="F92">
-        <v>13.6</v>
-      </c>
-      <c r="G92">
-        <v>25.3</v>
-      </c>
       <c r="H92" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I92" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J92" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K92" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L92" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="M92" s="1">
         <v>45615</v>
@@ -4833,26 +4275,20 @@
       <c r="E93" t="s">
         <v>16</v>
       </c>
-      <c r="F93">
-        <v>13.6</v>
-      </c>
-      <c r="G93">
-        <v>25.3</v>
-      </c>
       <c r="H93" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I93" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J93" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K93" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L93" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="M93" s="1">
         <v>45548</v>
@@ -4874,26 +4310,20 @@
       <c r="E94" t="s">
         <v>18</v>
       </c>
-      <c r="F94">
-        <v>15.6</v>
-      </c>
-      <c r="G94">
-        <v>32.4</v>
-      </c>
       <c r="H94" t="s">
         <v>35</v>
       </c>
       <c r="I94" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J94" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K94" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L94" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="M94" s="1">
         <v>45565</v>
@@ -4915,26 +4345,20 @@
       <c r="E95" t="s">
         <v>27</v>
       </c>
-      <c r="F95">
-        <v>13</v>
-      </c>
-      <c r="G95">
-        <v>33.5</v>
-      </c>
       <c r="H95" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I95" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J95" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K95" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L95" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="M95" s="1">
         <v>45566</v>
@@ -4956,26 +4380,20 @@
       <c r="E96" t="s">
         <v>24</v>
       </c>
-      <c r="F96">
-        <v>13.1</v>
-      </c>
-      <c r="G96">
-        <v>30.2</v>
-      </c>
       <c r="H96" t="s">
         <v>35</v>
       </c>
       <c r="I96" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J96" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K96" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="L96" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="M96" s="1">
         <v>45548</v>
@@ -4997,26 +4415,20 @@
       <c r="E97" t="s">
         <v>16</v>
       </c>
-      <c r="F97">
-        <v>13.6</v>
-      </c>
-      <c r="G97">
-        <v>25.3</v>
-      </c>
       <c r="H97" t="s">
         <v>35</v>
       </c>
       <c r="I97" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J97" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K97" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L97" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="M97" s="1">
         <v>45536</v>
@@ -5038,26 +4450,20 @@
       <c r="E98" t="s">
         <v>18</v>
       </c>
-      <c r="F98">
-        <v>15.6</v>
-      </c>
-      <c r="G98">
-        <v>32.4</v>
-      </c>
       <c r="H98" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I98" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J98" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K98" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L98" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="M98" s="1">
         <v>45548</v>
@@ -5079,26 +4485,20 @@
       <c r="E99" t="s">
         <v>25</v>
       </c>
-      <c r="F99">
-        <v>15.6</v>
-      </c>
-      <c r="G99">
-        <v>32.4</v>
-      </c>
       <c r="H99" t="s">
         <v>35</v>
       </c>
       <c r="I99" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J99" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K99" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L99" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="M99" s="1">
         <v>45536</v>
@@ -5120,26 +4520,20 @@
       <c r="E100" t="s">
         <v>16</v>
       </c>
-      <c r="F100">
-        <v>13.4</v>
-      </c>
-      <c r="G100">
-        <v>25.3</v>
-      </c>
       <c r="H100" t="s">
         <v>35</v>
       </c>
       <c r="I100" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="J100" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="K100" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="L100" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="M100" s="1">
         <v>45573</v>
@@ -5161,26 +4555,20 @@
       <c r="E101" t="s">
         <v>16</v>
       </c>
-      <c r="F101">
-        <v>13.9</v>
-      </c>
-      <c r="G101">
-        <v>23.7</v>
-      </c>
       <c r="H101" t="s">
         <v>35</v>
       </c>
       <c r="I101" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J101" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K101" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L101" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M101" s="1">
         <v>45527</v>
@@ -5202,26 +4590,20 @@
       <c r="E102" t="s">
         <v>16</v>
       </c>
-      <c r="F102">
-        <v>13.6</v>
-      </c>
-      <c r="G102">
-        <v>25.3</v>
-      </c>
       <c r="H102" t="s">
         <v>35</v>
       </c>
       <c r="I102" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J102" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K102" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L102" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="M102" s="1">
         <v>45527</v>
@@ -5243,26 +4625,20 @@
       <c r="E103" t="s">
         <v>16</v>
       </c>
-      <c r="F103">
-        <v>13.6</v>
-      </c>
-      <c r="G103">
-        <v>25.3</v>
-      </c>
       <c r="H103" t="s">
         <v>35</v>
       </c>
       <c r="I103" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J103" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K103" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L103" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="M103" s="1">
         <v>45564</v>
@@ -5284,26 +4660,20 @@
       <c r="E104" t="s">
         <v>27</v>
       </c>
-      <c r="F104">
-        <v>13.2</v>
-      </c>
-      <c r="G104">
-        <v>34.1</v>
-      </c>
       <c r="H104" t="s">
         <v>35</v>
       </c>
       <c r="I104" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J104" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K104" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L104" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="M104" s="1">
         <v>45565</v>
@@ -5325,26 +4695,20 @@
       <c r="E105" t="s">
         <v>16</v>
       </c>
-      <c r="F105">
-        <v>13.6</v>
-      </c>
-      <c r="G105">
-        <v>25.3</v>
-      </c>
       <c r="H105" t="s">
         <v>35</v>
       </c>
       <c r="I105" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J105" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K105" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L105" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="M105" s="1">
         <v>45527</v>
@@ -5366,26 +4730,20 @@
       <c r="E106" t="s">
         <v>29</v>
       </c>
-      <c r="F106">
-        <v>14.4</v>
-      </c>
-      <c r="G106">
-        <v>33.4</v>
-      </c>
       <c r="H106" t="s">
         <v>35</v>
       </c>
       <c r="I106" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J106" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K106" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L106" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="M106" s="1">
         <v>45526</v>
@@ -5407,26 +4765,20 @@
       <c r="E107" t="s">
         <v>20</v>
       </c>
-      <c r="F107">
-        <v>12</v>
-      </c>
-      <c r="G107">
-        <v>24.8</v>
-      </c>
       <c r="H107" t="s">
         <v>35</v>
       </c>
       <c r="I107" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="J107" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="K107" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="L107" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="M107" s="1">
         <v>45526</v>
@@ -5448,26 +4800,20 @@
       <c r="E108" t="s">
         <v>28</v>
       </c>
-      <c r="F108">
-        <v>13.4</v>
-      </c>
-      <c r="G108">
-        <v>22.4</v>
-      </c>
       <c r="H108" t="s">
         <v>35</v>
       </c>
       <c r="I108" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="J108" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="K108" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L108" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="M108" s="1">
         <v>45526</v>
@@ -5489,26 +4835,20 @@
       <c r="E109" t="s">
         <v>27</v>
       </c>
-      <c r="F109">
-        <v>13</v>
-      </c>
-      <c r="G109">
-        <v>33.5</v>
-      </c>
       <c r="H109" t="s">
         <v>35</v>
       </c>
       <c r="I109" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J109" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K109" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L109" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="M109" s="1">
         <v>45537</v>
@@ -5530,26 +4870,20 @@
       <c r="E110" t="s">
         <v>16</v>
       </c>
-      <c r="F110">
-        <v>13.6</v>
-      </c>
-      <c r="G110">
-        <v>25.3</v>
-      </c>
       <c r="H110" t="s">
         <v>35</v>
       </c>
       <c r="I110" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J110" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K110" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L110" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="M110" s="1">
         <v>45526</v>
@@ -5571,26 +4905,20 @@
       <c r="E111" t="s">
         <v>16</v>
       </c>
-      <c r="F111">
-        <v>13.6</v>
-      </c>
-      <c r="G111">
-        <v>25.3</v>
-      </c>
       <c r="H111" t="s">
         <v>35</v>
       </c>
       <c r="I111" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J111" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K111" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L111" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="M111" s="1">
         <v>45501</v>
@@ -5612,26 +4940,20 @@
       <c r="E112" t="s">
         <v>16</v>
       </c>
-      <c r="F112">
-        <v>13.6</v>
-      </c>
-      <c r="G112">
-        <v>25.3</v>
-      </c>
       <c r="H112" t="s">
         <v>35</v>
       </c>
       <c r="I112" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J112" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K112" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L112" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="M112" s="1">
         <v>45501</v>
@@ -5653,26 +4975,20 @@
       <c r="E113" t="s">
         <v>16</v>
       </c>
-      <c r="F113">
-        <v>13.6</v>
-      </c>
-      <c r="G113">
-        <v>25.3</v>
-      </c>
       <c r="H113" t="s">
         <v>35</v>
       </c>
       <c r="I113" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J113" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K113" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L113" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="M113" s="1">
         <v>45501</v>
@@ -5694,26 +5010,20 @@
       <c r="E114" t="s">
         <v>16</v>
       </c>
-      <c r="F114">
-        <v>13.6</v>
-      </c>
-      <c r="G114">
-        <v>25.3</v>
-      </c>
       <c r="H114" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I114" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J114" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K114" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L114" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="M114" s="1">
         <v>45548</v>
@@ -5735,26 +5045,20 @@
       <c r="E115" t="s">
         <v>16</v>
       </c>
-      <c r="F115">
-        <v>13.6</v>
-      </c>
-      <c r="G115">
-        <v>25.3</v>
-      </c>
       <c r="H115" t="s">
         <v>35</v>
       </c>
       <c r="I115" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J115" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K115" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L115" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="M115" s="1">
         <v>45499</v>
@@ -5776,26 +5080,20 @@
       <c r="E116" t="s">
         <v>16</v>
       </c>
-      <c r="F116">
-        <v>13.6</v>
-      </c>
-      <c r="G116">
-        <v>25.3</v>
-      </c>
       <c r="H116" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I116" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J116" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K116" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L116" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="M116" s="1">
         <v>45501</v>
@@ -5817,26 +5115,20 @@
       <c r="E117" t="s">
         <v>25</v>
       </c>
-      <c r="F117">
-        <v>15.6</v>
-      </c>
-      <c r="G117">
-        <v>32.4</v>
-      </c>
       <c r="H117" t="s">
         <v>35</v>
       </c>
       <c r="I117" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J117" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K117" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L117" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="M117" s="1">
         <v>45453</v>
@@ -5858,26 +5150,20 @@
       <c r="E118" t="s">
         <v>16</v>
       </c>
-      <c r="F118">
-        <v>13.6</v>
-      </c>
-      <c r="G118">
-        <v>25.3</v>
-      </c>
       <c r="H118" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I118" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J118" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K118" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L118" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="M118" s="1">
         <v>45498</v>
@@ -5899,26 +5185,20 @@
       <c r="E119" t="s">
         <v>25</v>
       </c>
-      <c r="F119">
-        <v>15.4</v>
-      </c>
-      <c r="G119">
-        <v>32.4</v>
-      </c>
       <c r="H119" t="s">
         <v>35</v>
       </c>
       <c r="I119" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J119" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K119" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="L119" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="M119" s="1">
         <v>45499</v>
@@ -5940,26 +5220,20 @@
       <c r="E120" t="s">
         <v>16</v>
       </c>
-      <c r="F120">
-        <v>13.6</v>
-      </c>
-      <c r="G120">
-        <v>25.3</v>
-      </c>
       <c r="H120" t="s">
         <v>35</v>
       </c>
       <c r="I120" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J120" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K120" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L120" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="M120" s="1">
         <v>45505</v>
@@ -5981,26 +5255,20 @@
       <c r="E121" t="s">
         <v>16</v>
       </c>
-      <c r="F121">
-        <v>13.6</v>
-      </c>
-      <c r="G121">
-        <v>25.3</v>
-      </c>
       <c r="H121" t="s">
         <v>35</v>
       </c>
       <c r="I121" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J121" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K121" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="L121" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="M121" s="1">
         <v>45527</v>
@@ -6022,26 +5290,20 @@
       <c r="E122" t="s">
         <v>16</v>
       </c>
-      <c r="F122">
-        <v>13.6</v>
-      </c>
-      <c r="G122">
-        <v>25.3</v>
-      </c>
       <c r="H122" t="s">
         <v>35</v>
       </c>
       <c r="I122" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J122" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K122" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="L122" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="M122" s="1">
         <v>45470</v>
@@ -6063,26 +5325,20 @@
       <c r="E123" t="s">
         <v>25</v>
       </c>
-      <c r="F123">
-        <v>15.4</v>
-      </c>
-      <c r="G123">
-        <v>32.4</v>
-      </c>
       <c r="H123" t="s">
         <v>35</v>
       </c>
       <c r="I123" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="J123" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K123" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L123" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="M123" s="1">
         <v>45499</v>
@@ -6104,26 +5360,20 @@
       <c r="E124" t="s">
         <v>16</v>
       </c>
-      <c r="F124">
-        <v>13.6</v>
-      </c>
-      <c r="G124">
-        <v>25.3</v>
-      </c>
       <c r="H124" t="s">
         <v>35</v>
       </c>
       <c r="I124" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J124" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K124" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="L124" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="M124" s="1">
         <v>45527</v>
@@ -6145,26 +5395,20 @@
       <c r="E125" t="s">
         <v>16</v>
       </c>
-      <c r="F125">
-        <v>14.2</v>
-      </c>
-      <c r="G125">
-        <v>24.6</v>
-      </c>
       <c r="H125" t="s">
         <v>35</v>
       </c>
       <c r="I125" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J125" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K125" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L125" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="M125" s="1">
         <v>45470</v>
@@ -6186,26 +5430,20 @@
       <c r="E126" t="s">
         <v>16</v>
       </c>
-      <c r="F126">
-        <v>13.6</v>
-      </c>
-      <c r="G126">
-        <v>25.3</v>
-      </c>
       <c r="H126" t="s">
         <v>35</v>
       </c>
       <c r="I126" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J126" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K126" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="L126" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="M126" s="1">
         <v>45453</v>
@@ -6227,26 +5465,20 @@
       <c r="E127" t="s">
         <v>16</v>
       </c>
-      <c r="F127">
-        <v>13.6</v>
-      </c>
-      <c r="G127">
-        <v>25.3</v>
-      </c>
       <c r="H127" t="s">
         <v>35</v>
       </c>
       <c r="I127" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J127" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K127" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="L127" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="M127" s="1">
         <v>45453</v>
@@ -6268,26 +5500,20 @@
       <c r="E128" t="s">
         <v>16</v>
       </c>
-      <c r="F128">
-        <v>13.6</v>
-      </c>
-      <c r="G128">
-        <v>25.3</v>
-      </c>
       <c r="H128" t="s">
         <v>35</v>
       </c>
       <c r="I128" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J128" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K128" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L128" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="M128" s="1">
         <v>45453</v>
@@ -6309,26 +5535,20 @@
       <c r="E129" t="s">
         <v>16</v>
       </c>
-      <c r="F129">
-        <v>13.6</v>
-      </c>
-      <c r="G129">
-        <v>25.3</v>
-      </c>
       <c r="H129" t="s">
         <v>35</v>
       </c>
       <c r="I129" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J129" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K129" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L129" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="M129" s="1">
         <v>45453</v>
@@ -6350,26 +5570,20 @@
       <c r="E130" t="s">
         <v>24</v>
       </c>
-      <c r="F130">
-        <v>12.9</v>
-      </c>
-      <c r="G130">
-        <v>31.6</v>
-      </c>
       <c r="H130" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I130" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J130" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K130" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L130" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="M130" s="1">
         <v>45481</v>
@@ -6391,26 +5605,20 @@
       <c r="E131" t="s">
         <v>16</v>
       </c>
-      <c r="F131">
-        <v>13.6</v>
-      </c>
-      <c r="G131">
-        <v>25.3</v>
-      </c>
       <c r="H131" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I131" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J131" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K131" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L131" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="M131" s="1">
         <v>41855</v>
@@ -6432,26 +5640,20 @@
       <c r="E132" t="s">
         <v>29</v>
       </c>
-      <c r="F132">
-        <v>14.3</v>
-      </c>
-      <c r="G132">
-        <v>33.5</v>
-      </c>
       <c r="H132" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I132" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J132" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K132" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L132" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="M132" s="1">
         <v>41969</v>
@@ -6473,26 +5675,20 @@
       <c r="E133" t="s">
         <v>16</v>
       </c>
-      <c r="F133">
-        <v>13.6</v>
-      </c>
-      <c r="G133">
-        <v>25.3</v>
-      </c>
       <c r="H133" t="s">
         <v>35</v>
       </c>
       <c r="I133" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="J133" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="K133" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="L133" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="M133" s="1">
         <v>45441</v>
@@ -6514,26 +5710,20 @@
       <c r="E134" t="s">
         <v>16</v>
       </c>
-      <c r="F134">
-        <v>13.6</v>
-      </c>
-      <c r="G134">
-        <v>25.3</v>
-      </c>
       <c r="H134" t="s">
         <v>35</v>
       </c>
       <c r="I134" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J134" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K134" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="L134" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="M134" s="1">
         <v>45478</v>
@@ -6555,26 +5745,20 @@
       <c r="E135" t="s">
         <v>24</v>
       </c>
-      <c r="F135">
-        <v>12.9</v>
-      </c>
-      <c r="G135">
-        <v>31.2</v>
-      </c>
       <c r="H135" t="s">
         <v>35</v>
       </c>
       <c r="I135" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J135" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K135" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L135" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="M135" s="1">
         <v>45482</v>
@@ -6596,26 +5780,20 @@
       <c r="E136" t="s">
         <v>18</v>
       </c>
-      <c r="F136">
-        <v>15.6</v>
-      </c>
-      <c r="G136">
-        <v>32.5</v>
-      </c>
       <c r="H136" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I136" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J136" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K136" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L136" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="M136" s="1">
         <v>45449</v>
@@ -6637,26 +5815,20 @@
       <c r="E137" t="s">
         <v>28</v>
       </c>
-      <c r="F137">
-        <v>12.7</v>
-      </c>
-      <c r="G137">
-        <v>22.4</v>
-      </c>
       <c r="H137" t="s">
         <v>35</v>
       </c>
       <c r="I137" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J137" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K137" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L137" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="M137" s="1">
         <v>45440</v>
@@ -6678,26 +5850,20 @@
       <c r="E138" t="s">
         <v>21</v>
       </c>
-      <c r="F138">
-        <v>11.4</v>
-      </c>
-      <c r="G138">
-        <v>30.1</v>
-      </c>
       <c r="H138" t="s">
         <v>35</v>
       </c>
       <c r="I138" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="J138" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="K138" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="L138" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="M138" s="1">
         <v>45435</v>
@@ -6719,26 +5885,20 @@
       <c r="E139" t="s">
         <v>16</v>
       </c>
-      <c r="F139">
-        <v>13.6</v>
-      </c>
-      <c r="G139">
-        <v>25.3</v>
-      </c>
       <c r="H139" t="s">
         <v>35</v>
       </c>
       <c r="I139" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J139" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K139" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="L139" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="M139" s="1">
         <v>45407</v>
@@ -6760,26 +5920,20 @@
       <c r="E140" t="s">
         <v>30</v>
       </c>
-      <c r="F140">
-        <v>14.5</v>
-      </c>
-      <c r="G140">
-        <v>32.2</v>
-      </c>
       <c r="H140" t="s">
         <v>35</v>
       </c>
       <c r="I140" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="J140" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="K140" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L140" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="M140" s="1">
         <v>45383</v>
@@ -6801,26 +5955,20 @@
       <c r="E141" t="s">
         <v>18</v>
       </c>
-      <c r="F141">
-        <v>15.6</v>
-      </c>
-      <c r="G141">
-        <v>32.5</v>
-      </c>
       <c r="H141" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I141" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J141" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K141" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L141" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="M141" s="1">
         <v>45374</v>
@@ -6842,26 +5990,20 @@
       <c r="E142" t="s">
         <v>20</v>
       </c>
-      <c r="F142">
-        <v>10.8</v>
-      </c>
-      <c r="G142">
-        <v>25.1</v>
-      </c>
       <c r="H142" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I142" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J142" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K142" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L142" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="M142" s="1">
         <v>45399</v>
@@ -6883,26 +6025,20 @@
       <c r="E143" t="s">
         <v>31</v>
       </c>
-      <c r="F143">
-        <v>9.4</v>
-      </c>
-      <c r="G143">
-        <v>28.6</v>
-      </c>
       <c r="H143" t="s">
         <v>35</v>
       </c>
       <c r="I143" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="J143" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="K143" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="L143" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="M143" s="1">
         <v>45371</v>
@@ -6924,26 +6060,20 @@
       <c r="E144" t="s">
         <v>32</v>
       </c>
-      <c r="F144">
-        <v>13.6</v>
-      </c>
-      <c r="G144">
-        <v>34.5</v>
-      </c>
       <c r="H144" t="s">
         <v>35</v>
       </c>
       <c r="I144" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="J144" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="K144" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L144" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="M144" s="1">
         <v>45374</v>
@@ -6965,26 +6095,20 @@
       <c r="E145" t="s">
         <v>32</v>
       </c>
-      <c r="F145">
-        <v>13.5</v>
-      </c>
-      <c r="G145">
-        <v>34.5</v>
-      </c>
       <c r="H145" t="s">
         <v>35</v>
       </c>
       <c r="I145" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="J145" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="K145" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L145" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="M145" s="1">
         <v>45360</v>
@@ -7006,26 +6130,20 @@
       <c r="E146" t="s">
         <v>25</v>
       </c>
-      <c r="F146">
-        <v>15.5</v>
-      </c>
-      <c r="G146">
-        <v>32.5</v>
-      </c>
       <c r="H146" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I146" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="J146" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="K146" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="L146" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="M146" s="1">
         <v>45427</v>
@@ -7047,26 +6165,20 @@
       <c r="E147" t="s">
         <v>24</v>
       </c>
-      <c r="F147">
-        <v>12.9</v>
-      </c>
-      <c r="G147">
-        <v>31.2</v>
-      </c>
       <c r="H147" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I147" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J147" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K147" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L147" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="M147" s="1">
         <v>45343</v>
@@ -7088,26 +6200,20 @@
       <c r="E148" t="s">
         <v>29</v>
       </c>
-      <c r="F148">
-        <v>14.3</v>
-      </c>
-      <c r="G148">
-        <v>33.5</v>
-      </c>
       <c r="H148" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I148" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="J148" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="K148" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L148" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="M148" s="1">
         <v>45334</v>
@@ -7129,26 +6235,20 @@
       <c r="E149" t="s">
         <v>29</v>
       </c>
-      <c r="F149">
-        <v>14.7</v>
-      </c>
-      <c r="G149">
-        <v>33.2</v>
-      </c>
       <c r="H149" t="s">
         <v>35</v>
       </c>
       <c r="I149" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J149" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K149" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L149" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="M149" s="1">
         <v>45301</v>
@@ -7170,26 +6270,20 @@
       <c r="E150" t="s">
         <v>18</v>
       </c>
-      <c r="F150">
-        <v>15.6</v>
-      </c>
-      <c r="G150">
-        <v>32.4</v>
-      </c>
       <c r="H150" t="s">
         <v>35</v>
       </c>
       <c r="I150" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J150" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K150" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L150" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="M150" s="1">
         <v>45301</v>
@@ -7211,26 +6305,20 @@
       <c r="E151" t="s">
         <v>20</v>
       </c>
-      <c r="F151">
-        <v>12</v>
-      </c>
-      <c r="G151">
-        <v>24.8</v>
-      </c>
       <c r="H151" t="s">
         <v>35</v>
       </c>
       <c r="I151" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="J151" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="K151" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="L151" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="M151" s="1">
         <v>45257</v>
@@ -7252,26 +6340,20 @@
       <c r="E152" t="s">
         <v>16</v>
       </c>
-      <c r="F152">
-        <v>13.6</v>
-      </c>
-      <c r="G152">
-        <v>25.3</v>
-      </c>
       <c r="H152" t="s">
         <v>35</v>
       </c>
       <c r="I152" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="J152" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="K152" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L152" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="M152" s="1">
         <v>45227</v>
@@ -7293,26 +6375,20 @@
       <c r="E153" t="s">
         <v>20</v>
       </c>
-      <c r="F153">
-        <v>12</v>
-      </c>
-      <c r="G153">
-        <v>24.8</v>
-      </c>
       <c r="H153" t="s">
         <v>35</v>
       </c>
       <c r="I153" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="J153" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="K153" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="L153" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="M153" s="1">
         <v>45197</v>
@@ -7334,26 +6410,20 @@
       <c r="E154" t="s">
         <v>26</v>
       </c>
-      <c r="F154">
-        <v>12.9</v>
-      </c>
-      <c r="G154">
-        <v>23.4</v>
-      </c>
       <c r="H154" t="s">
         <v>35</v>
       </c>
       <c r="I154" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="J154" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="K154" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L154" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="M154" s="1">
         <v>45188</v>
@@ -7375,26 +6445,20 @@
       <c r="E155" t="s">
         <v>20</v>
       </c>
-      <c r="F155">
-        <v>11</v>
-      </c>
-      <c r="G155">
-        <v>25</v>
-      </c>
       <c r="H155" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I155" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="J155" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="K155" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L155" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="M155" s="1">
         <v>45131</v>
@@ -7416,26 +6480,20 @@
       <c r="E156" t="s">
         <v>25</v>
       </c>
-      <c r="F156">
-        <v>15.6</v>
-      </c>
-      <c r="G156">
-        <v>32.4</v>
-      </c>
       <c r="H156" t="s">
         <v>35</v>
       </c>
       <c r="I156" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="J156" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="K156" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L156" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="M156" s="1">
         <v>45131</v>
@@ -7457,26 +6515,20 @@
       <c r="E157" t="s">
         <v>25</v>
       </c>
-      <c r="F157">
-        <v>15.6</v>
-      </c>
-      <c r="G157">
-        <v>32.4</v>
-      </c>
       <c r="H157" t="s">
         <v>35</v>
       </c>
       <c r="I157" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J157" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K157" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L157" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="M157" s="1">
         <v>45069</v>
@@ -7498,26 +6550,20 @@
       <c r="E158" t="s">
         <v>25</v>
       </c>
-      <c r="F158">
-        <v>15.6</v>
-      </c>
-      <c r="G158">
-        <v>32.4</v>
-      </c>
       <c r="H158" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I158" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="J158" t="s">
+        <v>53</v>
+      </c>
+      <c r="K158" t="s">
         <v>57</v>
       </c>
-      <c r="K158" t="s">
-        <v>61</v>
-      </c>
       <c r="L158" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="M158" s="1">
         <v>45263</v>
@@ -7539,26 +6585,20 @@
       <c r="E159" t="s">
         <v>25</v>
       </c>
-      <c r="F159">
-        <v>15.6</v>
-      </c>
-      <c r="G159">
-        <v>32.4</v>
-      </c>
       <c r="H159" t="s">
         <v>35</v>
       </c>
       <c r="I159" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J159" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K159" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L159" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="M159" s="1">
         <v>45069</v>
@@ -7580,26 +6620,20 @@
       <c r="E160" t="s">
         <v>25</v>
       </c>
-      <c r="F160">
-        <v>15.4</v>
-      </c>
-      <c r="G160">
-        <v>32.4</v>
-      </c>
       <c r="H160" t="s">
         <v>35</v>
       </c>
       <c r="I160" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J160" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K160" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="L160" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="M160" s="1">
         <v>45041</v>
@@ -7621,26 +6655,20 @@
       <c r="E161" t="s">
         <v>25</v>
       </c>
-      <c r="F161">
-        <v>15.5</v>
-      </c>
-      <c r="G161">
-        <v>32.5</v>
-      </c>
       <c r="H161" t="s">
         <v>35</v>
       </c>
       <c r="I161" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J161" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K161" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L161" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="M161" s="1">
         <v>45040</v>
@@ -7662,26 +6690,20 @@
       <c r="E162" t="s">
         <v>21</v>
       </c>
-      <c r="F162">
-        <v>11.9</v>
-      </c>
-      <c r="G162">
-        <v>30</v>
-      </c>
       <c r="H162" t="s">
         <v>35</v>
       </c>
       <c r="I162" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J162" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K162" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L162" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="M162" s="1">
         <v>45807</v>
@@ -7703,26 +6725,20 @@
       <c r="E163" t="s">
         <v>33</v>
       </c>
-      <c r="F163">
-        <v>11.4</v>
-      </c>
-      <c r="G163">
-        <v>30.8</v>
-      </c>
       <c r="H163" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I163" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="J163" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="K163" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L163" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="M163" s="1">
         <v>44813</v>
@@ -7744,26 +6760,20 @@
       <c r="E164" t="s">
         <v>16</v>
       </c>
-      <c r="F164">
-        <v>13.6</v>
-      </c>
-      <c r="G164">
-        <v>25.3</v>
-      </c>
       <c r="H164" t="s">
         <v>35</v>
       </c>
       <c r="I164" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="J164" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K164" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L164" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="M164" s="1">
         <v>44653</v>
@@ -7785,26 +6795,20 @@
       <c r="E165" t="s">
         <v>34</v>
       </c>
-      <c r="F165">
-        <v>19.6</v>
-      </c>
-      <c r="G165">
-        <v>37.2</v>
-      </c>
       <c r="H165" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I165" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="J165" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="K165" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L165" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="M165" s="1">
         <v>44641</v>
@@ -7826,26 +6830,20 @@
       <c r="E166" t="s">
         <v>29</v>
       </c>
-      <c r="F166">
-        <v>14.3</v>
-      </c>
-      <c r="G166">
-        <v>33.5</v>
-      </c>
       <c r="H166" t="s">
         <v>35</v>
       </c>
       <c r="I166" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="J166" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="K166" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L166" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="M166" s="1">
         <v>44622</v>
